--- a/artfynd/A 11693-2025 artfynd.xlsx
+++ b/artfynd/A 11693-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,44 +792,36 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96246912</v>
+        <v>136760057</v>
       </c>
       <c r="B3" t="n">
-        <v>87491</v>
+        <v>87385</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cinnoberspindling</t>
+          <t>Blå lökspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius cinnabarinus</t>
+          <t>Cortinarius caerulescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -838,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443242</v>
+        <v>443187</v>
       </c>
       <c r="R3" t="n">
-        <v>6180226</v>
+        <v>6180207</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-18</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-18</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,74 +878,76 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Ädellövskog i ravin längs bäck.</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Patrik Celander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tony Svensson, Anders Wånge Kjellsson, Charlotte Wigermo, Krister Wadén, Shu-Chin Hysing, Ulla Berglund</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Puggehatten, exkursion</t>
-        </is>
-      </c>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96246912</t>
+          <t>https://artportalen.se/Sighting/136760057</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106564607</v>
+        <v>96246912</v>
       </c>
       <c r="B4" t="n">
-        <v>87248</v>
+        <v>87491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kejsarspindling</t>
+          <t>Cinnoberspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius elegantissimus</t>
+          <t>Cortinarius cinnabarinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Myrestad, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443266</v>
+        <v>443242</v>
       </c>
       <c r="R4" t="n">
-        <v>6180230</v>
+        <v>6180226</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,27 +974,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-10-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:15</t>
+          <t>2021-09-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-10-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Luktar kräftspad</t>
+          <t>2021-09-18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,24 +988,24 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AR4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Ädellövskog i ravin längs bäck.</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sigvard Svensson</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sigvard Svensson, Charlotte Wigermo, Tony Svensson, Joachim Krumlinde, Ulla Berglund, Jan Svensson</t>
+          <t>Tony Svensson, Anders Wånge Kjellsson, Charlotte Wigermo, Krister Wadén, Shu-Chin Hysing, Ulla Berglund</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1036,13 +1015,13 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106564607</t>
+          <t>https://artportalen.se/Sighting/96246912</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128856480</v>
+        <v>106564607</v>
       </c>
       <c r="B5" t="n">
         <v>87248</v>
@@ -1077,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>443176</v>
+        <v>443266</v>
       </c>
       <c r="R5" t="n">
-        <v>6180189</v>
+        <v>6180230</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,12 +1086,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2016-10-01</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2016-10-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Luktar kräftspad</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,45 +1115,40 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Bokskog</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
-        </is>
       </c>
       <c r="AR5" t="inlineStr"/>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Sigvard Svensson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ward Tamsyn, Mattias Andersson, Karin Hjelmér, Olle Amcoff, Anders Wånge Kjellsson, Oskar Karl Elias Olsson, Hans Rydberg, Martin Peraic, Margaux Boeraeve, Claes Ingvert, Cecilia  Wånge , Ulf Gärdenfors</t>
+          <t>Sigvard Svensson, Charlotte Wigermo, Tony Svensson, Joachim Krumlinde, Ulla Berglund, Jan Svensson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>SMF:s mykologivecka</t>
+          <t>Puggehatten, exkursion</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128856480</t>
+          <t>https://artportalen.se/Sighting/106564607</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128891669</v>
+        <v>128856480</v>
       </c>
       <c r="B6" t="n">
         <v>87248</v>
@@ -1194,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>443206</v>
+        <v>443176</v>
       </c>
       <c r="R6" t="n">
-        <v>6180223</v>
+        <v>6180189</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1241,9 +1230,14 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Bok</t>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Bokskog</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr"/>
@@ -1265,60 +1259,51 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128891669</t>
+          <t>https://artportalen.se/Sighting/128856480</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>61983788</v>
+        <v>128891669</v>
       </c>
       <c r="B7" t="n">
-        <v>87394</v>
+        <v>87248</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>474</v>
+        <v>447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rävspindling</t>
+          <t>Kejsarspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius vulpinus</t>
+          <t>Cortinarius elegantissimus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Velen.) Rob.Henry</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Myrestad, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>443183</v>
+        <v>443206</v>
       </c>
       <c r="R7" t="n">
-        <v>6180192</v>
+        <v>6180223</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,17 +1330,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2016-10-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2016-10-30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>1 fruktkropp.</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,32 +1347,37 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Bokskog, sluttning</t>
-        </is>
-      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bok</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Örjan Fritz, Tony Svensson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Ward Tamsyn, Mattias Andersson, Karin Hjelmér, Olle Amcoff, Anders Wånge Kjellsson, Oskar Karl Elias Olsson, Hans Rydberg, Martin Peraic, Margaux Boeraeve, Claes Ingvert, Cecilia  Wånge , Ulf Gärdenfors</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61983788</t>
+          <t>https://artportalen.se/Sighting/128891669</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>61983789</v>
+        <v>61983788</v>
       </c>
       <c r="B8" t="n">
         <v>87394</v>
@@ -1436,10 +1421,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>443191</v>
+        <v>443183</v>
       </c>
       <c r="R8" t="n">
-        <v>6180214</v>
+        <v>6180192</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1507,13 +1492,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61983789</t>
+          <t>https://artportalen.se/Sighting/61983788</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>62416653</v>
+        <v>61983789</v>
       </c>
       <c r="B9" t="n">
         <v>87394</v>
@@ -1548,23 +1533,22 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Myrestad, 500 m OSO, Sk</t>
+          <t>Myrestad, Sk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>443214</v>
+        <v>443191</v>
       </c>
       <c r="R9" t="n">
-        <v>6180226</v>
+        <v>6180214</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1588,17 +1572,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2016-10-01</t>
+          <t>2016-10-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2016-10-01</t>
+          <t>2016-10-30</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Exkursion Puggehatten</t>
+          <t>1 fruktkropp.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,59 +1591,73 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Bokskog, sluttning</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Sigvard Svensson, Tony Svensson, Joachim Krumlinde, Ulla Berglund, Jan Svensson</t>
+          <t>Örjan Fritz, Tony Svensson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62416653</t>
+          <t>https://artportalen.se/Sighting/61983789</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>62417831</v>
+        <v>62416653</v>
       </c>
       <c r="B10" t="n">
-        <v>88424</v>
+        <v>87394</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1008</v>
+        <v>474</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Igelkottsröksvamp</t>
+          <t>Rävspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycoperdon echinatum</t>
+          <t>Cortinarius vulpinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Velen.) Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Myrestad, 500 m OSO, Sk</t>
@@ -1715,13 +1713,9 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>bokskog i bäckravin</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1737,57 +1731,54 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62417831</t>
+          <t>https://artportalen.se/Sighting/62416653</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113793290</v>
+        <v>62417831</v>
       </c>
       <c r="B11" t="n">
-        <v>75379</v>
+        <v>88424</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1118</v>
+        <v>1008</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Lycoperdon echinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tingalycka, Sk</t>
+          <t>Myrestad, 500 m OSO, Sk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443195</v>
+        <v>443214</v>
       </c>
       <c r="R11" t="n">
-        <v>6180204</v>
+        <v>6180226</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1811,12 +1802,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-12-30</t>
+          <t>2016-10-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-12-30</t>
+          <t>2016-10-01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Exkursion Puggehatten</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,49 +1821,38 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>bok</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica</t>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>bokskog i bäckravin</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Patrik Celander</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Patrik Celander</t>
+          <t>Charlotte Wigermo, Sigvard Svensson, Tony Svensson, Joachim Krumlinde, Ulla Berglund, Jan Svensson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113793290</t>
+          <t>https://artportalen.se/Sighting/62417831</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113793305</v>
+        <v>113793290</v>
       </c>
       <c r="B12" t="n">
-        <v>77726</v>
+        <v>75379</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,21 +1860,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1342</v>
+        <v>1118</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1902,13 +1887,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443160</v>
+        <v>443195</v>
       </c>
       <c r="R12" t="n">
-        <v>6180189</v>
+        <v>6180204</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1979,44 +1964,43 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113793305</t>
+          <t>https://artportalen.se/Sighting/113793290</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113793311</v>
+        <v>113793305</v>
       </c>
       <c r="B13" t="n">
-        <v>97811</v>
+        <v>77726</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2604</v>
+        <v>1342</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2101,65 +2085,58 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113793311</t>
+          <t>https://artportalen.se/Sighting/113793305</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>96246923</v>
+        <v>113793311</v>
       </c>
       <c r="B14" t="n">
-        <v>87365</v>
+        <v>97811</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3562</v>
+        <v>2604</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nunnespindling</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius subalbescens</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Reumaux</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Pfeiff.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Myrestad, Sk</t>
+          <t>Tingalycka, Sk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443202</v>
+        <v>443160</v>
       </c>
       <c r="R14" t="n">
-        <v>6180215</v>
+        <v>6180189</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2183,17 +2160,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-09-18</t>
+          <t>2023-12-30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-09-18</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Sporer tydligt mandelformade 9 x 5 um.</t>
+          <t>2023-12-30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2202,47 +2174,49 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Ädellövskog i ravin längs bäck.</t>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Patrik Celander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tony Svensson, Anders Wånge Kjellsson, Charlotte Wigermo, Krister Wadén, Shu-Chin Hysing, Ulla Berglund</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Puggehatten, exkursion</t>
-        </is>
-      </c>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96246923</t>
+          <t>https://artportalen.se/Sighting/113793311</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129541501</v>
+        <v>96246923</v>
       </c>
       <c r="B15" t="n">
-        <v>87352</v>
+        <v>87365</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2250,25 +2224,33 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>248950</v>
+        <v>3562</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Själlandsspindling</t>
+          <t>Nunnespindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius selandicus</t>
+          <t>Cortinarius subalbescens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Frøslev &amp; T.S.Jeppesen</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>Reumaux</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2277,13 +2259,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443288</v>
+        <v>443202</v>
       </c>
       <c r="R15" t="n">
-        <v>6180031</v>
+        <v>6180215</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2307,12 +2289,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2021-09-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2021-09-18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Sporer tydligt mandelformade 9 x 5 um.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2321,23 +2308,248 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Ädellövskog i ravin längs bäck.</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tony Svensson, Anders Wånge Kjellsson, Charlotte Wigermo, Krister Wadén, Shu-Chin Hysing, Ulla Berglund</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Puggehatten, exkursion</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96246923</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136760111</v>
+      </c>
+      <c r="B16" t="n">
+        <v>87539</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3562</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nunnespindling</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cortinarius subalbescens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Reumaux</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Myrestad, Sk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>443231</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6180213</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Maglehem</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136760111</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129541501</v>
+      </c>
+      <c r="B17" t="n">
+        <v>87352</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>248950</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Själlandsspindling</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Cortinarius selandicus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; T.S.Jeppesen</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Myrestad, Sk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>443288</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6180031</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Maglehem</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>Sofia Lund</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Sofia Lund, Tony Svensson, Mats Karlsson</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr">
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129541501</t>
         </is>
@@ -2359,6 +2571,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11693-2025 artfynd.xlsx
+++ b/artfynd/A 11693-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ17"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,7 +795,7 @@
         <v>136760057</v>
       </c>
       <c r="B3" t="n">
-        <v>87385</v>
+        <v>87387</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1021,48 +1021,51 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106564607</v>
+        <v>136761654</v>
       </c>
       <c r="B5" t="n">
-        <v>87248</v>
+        <v>87332</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kejsarspindling</t>
+          <t>Juvelspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius elegantissimus</t>
+          <t>Cortinarius croceocaeruleus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Pers. : Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Myrestad, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>443266</v>
+        <v>443197</v>
       </c>
       <c r="R5" t="n">
-        <v>6180230</v>
+        <v>6180221</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,27 +1089,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2016-10-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2016-10-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Luktar kräftspad</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,40 +1103,31 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AR5" t="inlineStr"/>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sigvard Svensson</t>
+          <t>Patrik Celander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sigvard Svensson, Charlotte Wigermo, Tony Svensson, Joachim Krumlinde, Ulla Berglund, Jan Svensson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Puggehatten, exkursion</t>
-        </is>
-      </c>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106564607</t>
+          <t>https://artportalen.se/Sighting/136761654</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128856480</v>
+        <v>106564607</v>
       </c>
       <c r="B6" t="n">
         <v>87248</v>
@@ -1183,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>443176</v>
+        <v>443266</v>
       </c>
       <c r="R6" t="n">
-        <v>6180189</v>
+        <v>6180230</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,12 +1192,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2016-10-01</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2016-10-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Luktar kräftspad</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,45 +1221,40 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Bokskog</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
-        </is>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Sigvard Svensson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ward Tamsyn, Mattias Andersson, Karin Hjelmér, Olle Amcoff, Anders Wånge Kjellsson, Oskar Karl Elias Olsson, Hans Rydberg, Martin Peraic, Margaux Boeraeve, Claes Ingvert, Cecilia  Wånge , Ulf Gärdenfors</t>
+          <t>Sigvard Svensson, Charlotte Wigermo, Tony Svensson, Joachim Krumlinde, Ulla Berglund, Jan Svensson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>SMF:s mykologivecka</t>
+          <t>Puggehatten, exkursion</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128856480</t>
+          <t>https://artportalen.se/Sighting/106564607</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128891669</v>
+        <v>128856480</v>
       </c>
       <c r="B7" t="n">
         <v>87248</v>
@@ -1300,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>443206</v>
+        <v>443176</v>
       </c>
       <c r="R7" t="n">
-        <v>6180223</v>
+        <v>6180189</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,9 +1336,14 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bok</t>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Bokskog</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr"/>
@@ -1371,60 +1365,51 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128891669</t>
+          <t>https://artportalen.se/Sighting/128856480</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>61983788</v>
+        <v>128891669</v>
       </c>
       <c r="B8" t="n">
-        <v>87394</v>
+        <v>87248</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>474</v>
+        <v>447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rävspindling</t>
+          <t>Kejsarspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius vulpinus</t>
+          <t>Cortinarius elegantissimus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Velen.) Rob.Henry</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Myrestad, Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>443183</v>
+        <v>443206</v>
       </c>
       <c r="R8" t="n">
-        <v>6180192</v>
+        <v>6180223</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,17 +1436,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2016-10-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2016-10-30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>1 fruktkropp.</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,32 +1453,37 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Bokskog, sluttning</t>
-        </is>
-      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bok</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Örjan Fritz, Tony Svensson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Ward Tamsyn, Mattias Andersson, Karin Hjelmér, Olle Amcoff, Anders Wånge Kjellsson, Oskar Karl Elias Olsson, Hans Rydberg, Martin Peraic, Margaux Boeraeve, Claes Ingvert, Cecilia  Wånge , Ulf Gärdenfors</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61983788</t>
+          <t>https://artportalen.se/Sighting/128891669</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>61983789</v>
+        <v>61983788</v>
       </c>
       <c r="B9" t="n">
         <v>87394</v>
@@ -1542,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>443191</v>
+        <v>443183</v>
       </c>
       <c r="R9" t="n">
-        <v>6180214</v>
+        <v>6180192</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1613,13 +1598,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61983789</t>
+          <t>https://artportalen.se/Sighting/61983788</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>62416653</v>
+        <v>61983789</v>
       </c>
       <c r="B10" t="n">
         <v>87394</v>
@@ -1654,23 +1639,22 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Myrestad, 500 m OSO, Sk</t>
+          <t>Myrestad, Sk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>443214</v>
+        <v>443191</v>
       </c>
       <c r="R10" t="n">
-        <v>6180226</v>
+        <v>6180214</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1694,17 +1678,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2016-10-01</t>
+          <t>2016-10-30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2016-10-01</t>
+          <t>2016-10-30</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Exkursion Puggehatten</t>
+          <t>1 fruktkropp.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,59 +1697,73 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Bokskog, sluttning</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Sigvard Svensson, Tony Svensson, Joachim Krumlinde, Ulla Berglund, Jan Svensson</t>
+          <t>Örjan Fritz, Tony Svensson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62416653</t>
+          <t>https://artportalen.se/Sighting/61983789</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>62417831</v>
+        <v>62416653</v>
       </c>
       <c r="B11" t="n">
-        <v>88424</v>
+        <v>87394</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1008</v>
+        <v>474</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Igelkottsröksvamp</t>
+          <t>Rävspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycoperdon echinatum</t>
+          <t>Cortinarius vulpinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Velen.) Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Myrestad, 500 m OSO, Sk</t>
@@ -1821,13 +1819,9 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>bokskog i bäckravin</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1843,57 +1837,54 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62417831</t>
+          <t>https://artportalen.se/Sighting/62416653</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113793290</v>
+        <v>62417831</v>
       </c>
       <c r="B12" t="n">
-        <v>75379</v>
+        <v>88424</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1118</v>
+        <v>1008</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Lycoperdon echinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tingalycka, Sk</t>
+          <t>Myrestad, 500 m OSO, Sk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443195</v>
+        <v>443214</v>
       </c>
       <c r="R12" t="n">
-        <v>6180204</v>
+        <v>6180226</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1917,12 +1908,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-12-30</t>
+          <t>2016-10-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-12-30</t>
+          <t>2016-10-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Exkursion Puggehatten</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,49 +1927,38 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>bok</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica</t>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>bokskog i bäckravin</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Patrik Celander</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Patrik Celander</t>
+          <t>Charlotte Wigermo, Sigvard Svensson, Tony Svensson, Joachim Krumlinde, Ulla Berglund, Jan Svensson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113793290</t>
+          <t>https://artportalen.se/Sighting/62417831</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113793305</v>
+        <v>113793290</v>
       </c>
       <c r="B13" t="n">
-        <v>77726</v>
+        <v>75379</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1981,21 +1966,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1342</v>
+        <v>1118</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2008,13 +1993,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>443160</v>
+        <v>443195</v>
       </c>
       <c r="R13" t="n">
-        <v>6180189</v>
+        <v>6180204</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2085,44 +2070,43 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113793305</t>
+          <t>https://artportalen.se/Sighting/113793290</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113793311</v>
+        <v>113793305</v>
       </c>
       <c r="B14" t="n">
-        <v>97811</v>
+        <v>77726</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2604</v>
+        <v>1342</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2207,65 +2191,58 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113793311</t>
+          <t>https://artportalen.se/Sighting/113793305</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>96246923</v>
+        <v>113793311</v>
       </c>
       <c r="B15" t="n">
-        <v>87365</v>
+        <v>97811</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3562</v>
+        <v>2604</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nunnespindling</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius subalbescens</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Reumaux</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Pfeiff.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Myrestad, Sk</t>
+          <t>Tingalycka, Sk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443202</v>
+        <v>443160</v>
       </c>
       <c r="R15" t="n">
-        <v>6180215</v>
+        <v>6180189</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2289,17 +2266,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-09-18</t>
+          <t>2023-12-30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-09-18</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Sporer tydligt mandelformade 9 x 5 um.</t>
+          <t>2023-12-30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2308,47 +2280,49 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Ädellövskog i ravin längs bäck.</t>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Patrik Celander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tony Svensson, Anders Wånge Kjellsson, Charlotte Wigermo, Krister Wadén, Shu-Chin Hysing, Ulla Berglund</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Puggehatten, exkursion</t>
-        </is>
-      </c>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96246923</t>
+          <t>https://artportalen.se/Sighting/113793311</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136760111</v>
+        <v>96246923</v>
       </c>
       <c r="B16" t="n">
-        <v>87539</v>
+        <v>87365</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,8 +2347,16 @@
           <t>Reumaux</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
@@ -2383,13 +2365,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443231</v>
+        <v>443202</v>
       </c>
       <c r="R16" t="n">
-        <v>6180213</v>
+        <v>6180215</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2413,12 +2395,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2021-09-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2021-09-18</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Sporer tydligt mandelformade 9 x 5 um.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2427,34 +2414,47 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Ädellövskog i ravin längs bäck.</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Patrik Celander</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Patrik Celander</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Tony Svensson, Anders Wånge Kjellsson, Charlotte Wigermo, Krister Wadén, Shu-Chin Hysing, Ulla Berglund</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Puggehatten, exkursion</t>
+        </is>
+      </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136760111</t>
+          <t>https://artportalen.se/Sighting/96246923</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129541501</v>
+        <v>136760111</v>
       </c>
       <c r="B17" t="n">
-        <v>87352</v>
+        <v>87541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2462,21 +2462,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>248950</v>
+        <v>3562</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Själlandsspindling</t>
+          <t>Nunnespindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius selandicus</t>
+          <t>Cortinarius subalbescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Frøslev &amp; T.S.Jeppesen</t>
+          <t>Reumaux</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2489,13 +2489,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>443288</v>
+        <v>443231</v>
       </c>
       <c r="R17" t="n">
-        <v>6180031</v>
+        <v>6180213</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2540,16 +2540,122 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Sofia Lund</t>
+          <t>Patrik Celander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sofia Lund, Tony Svensson, Mats Karlsson</t>
+          <t>Patrik Celander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136760111</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129541501</v>
+      </c>
+      <c r="B18" t="n">
+        <v>87352</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>248950</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Själlandsspindling</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Cortinarius selandicus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; T.S.Jeppesen</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Myrestad, Sk</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>443288</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6180031</v>
+      </c>
+      <c r="S18" t="n">
+        <v>50</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Maglehem</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Sofia Lund, Tony Svensson, Mats Karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129541501</t>
         </is>
@@ -2573,6 +2679,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11693-2025 artfynd.xlsx
+++ b/artfynd/A 11693-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136760057</v>
       </c>
       <c r="B3" t="n">
-        <v>87387</v>
+        <v>87389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136761654</v>
       </c>
       <c r="B5" t="n">
-        <v>87332</v>
+        <v>87334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>136760111</v>
       </c>
       <c r="B17" t="n">
-        <v>87541</v>
+        <v>87543</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 11693-2025 artfynd.xlsx
+++ b/artfynd/A 11693-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136760057</v>
       </c>
       <c r="B3" t="n">
-        <v>87389</v>
+        <v>87391</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136761654</v>
       </c>
       <c r="B5" t="n">
-        <v>87334</v>
+        <v>87336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>136760111</v>
       </c>
       <c r="B17" t="n">
-        <v>87543</v>
+        <v>87545</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 11693-2025 artfynd.xlsx
+++ b/artfynd/A 11693-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136760057</v>
       </c>
       <c r="B3" t="n">
-        <v>87391</v>
+        <v>87393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136761654</v>
       </c>
       <c r="B5" t="n">
-        <v>87336</v>
+        <v>87338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>136760111</v>
       </c>
       <c r="B17" t="n">
-        <v>87545</v>
+        <v>87547</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 11693-2025 artfynd.xlsx
+++ b/artfynd/A 11693-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136760057</v>
       </c>
       <c r="B3" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136761654</v>
       </c>
       <c r="B5" t="n">
-        <v>87338</v>
+        <v>87339</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>136760111</v>
       </c>
       <c r="B17" t="n">
-        <v>87547</v>
+        <v>87548</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 11693-2025 artfynd.xlsx
+++ b/artfynd/A 11693-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136760057</v>
       </c>
       <c r="B3" t="n">
-        <v>87394</v>
+        <v>87400</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136761654</v>
       </c>
       <c r="B5" t="n">
-        <v>87339</v>
+        <v>87345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>136760111</v>
       </c>
       <c r="B17" t="n">
-        <v>87548</v>
+        <v>87554</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 11693-2025 artfynd.xlsx
+++ b/artfynd/A 11693-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136760057</v>
       </c>
       <c r="B3" t="n">
-        <v>87400</v>
+        <v>87404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136761654</v>
       </c>
       <c r="B5" t="n">
-        <v>87345</v>
+        <v>87349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>136760111</v>
       </c>
       <c r="B17" t="n">
-        <v>87554</v>
+        <v>87558</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 11693-2025 artfynd.xlsx
+++ b/artfynd/A 11693-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136760057</v>
       </c>
       <c r="B3" t="n">
-        <v>87404</v>
+        <v>87406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136761654</v>
       </c>
       <c r="B5" t="n">
-        <v>87349</v>
+        <v>87351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>136760111</v>
       </c>
       <c r="B17" t="n">
-        <v>87558</v>
+        <v>87560</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 11693-2025 artfynd.xlsx
+++ b/artfynd/A 11693-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136760057</v>
       </c>
       <c r="B3" t="n">
-        <v>87406</v>
+        <v>87419</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136761654</v>
       </c>
       <c r="B5" t="n">
-        <v>87351</v>
+        <v>87364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>136760111</v>
       </c>
       <c r="B17" t="n">
-        <v>87560</v>
+        <v>87573</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 11693-2025 artfynd.xlsx
+++ b/artfynd/A 11693-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136760057</v>
       </c>
       <c r="B3" t="n">
-        <v>87419</v>
+        <v>87421</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136761654</v>
       </c>
       <c r="B5" t="n">
-        <v>87364</v>
+        <v>87366</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>136760111</v>
       </c>
       <c r="B17" t="n">
-        <v>87573</v>
+        <v>87575</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 11693-2025 artfynd.xlsx
+++ b/artfynd/A 11693-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136760057</v>
       </c>
       <c r="B3" t="n">
-        <v>87421</v>
+        <v>87424</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136761654</v>
       </c>
       <c r="B5" t="n">
-        <v>87366</v>
+        <v>87369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>136760111</v>
       </c>
       <c r="B17" t="n">
-        <v>87575</v>
+        <v>87578</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 11693-2025 artfynd.xlsx
+++ b/artfynd/A 11693-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136760057</v>
       </c>
       <c r="B3" t="n">
-        <v>87424</v>
+        <v>87434</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136761654</v>
       </c>
       <c r="B5" t="n">
-        <v>87369</v>
+        <v>87379</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>136760111</v>
       </c>
       <c r="B17" t="n">
-        <v>87578</v>
+        <v>87588</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 11693-2025 artfynd.xlsx
+++ b/artfynd/A 11693-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136760057</v>
       </c>
       <c r="B3" t="n">
-        <v>87434</v>
+        <v>87435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136761654</v>
       </c>
       <c r="B5" t="n">
-        <v>87379</v>
+        <v>87380</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>136760111</v>
       </c>
       <c r="B17" t="n">
-        <v>87588</v>
+        <v>87589</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 11693-2025 artfynd.xlsx
+++ b/artfynd/A 11693-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>136761654</v>
       </c>
       <c r="B5" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
